--- a/important_mails_2026-05-12.xlsx
+++ b/important_mails_2026-05-12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1190,7 +1190,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1205,72 +1205,21 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tue, 5 May 2026 17:50:39 +0000</t>
+          <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
+          <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 06/03/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0DRTR7GYJ
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-1583298956134227</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 12:21:34 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -1292,39 +1241,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1346,39 +1295,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1397,39 +1346,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1441,39 +1390,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1485,39 +1434,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -1529,39 +1478,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1573,39 +1522,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1617,39 +1566,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1661,39 +1610,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1712,39 +1661,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1763,39 +1712,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -1807,39 +1756,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1851,39 +1800,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1895,39 +1844,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1939,39 +1888,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -1983,39 +1932,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2027,39 +1976,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2071,39 +2020,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2115,39 +2064,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2159,39 +2108,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2203,39 +2152,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2247,39 +2196,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2291,39 +2240,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2335,40 +2284,40 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2387,39 +2336,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2431,39 +2380,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2475,39 +2424,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2519,39 +2468,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2563,39 +2512,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2607,39 +2556,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2660,39 +2609,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2707,39 +2656,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2758,39 +2707,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2814,39 +2763,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2869,39 +2818,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -2910,39 +2859,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2962,39 +2911,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3014,39 +2963,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -3062,39 +3011,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3114,39 +3063,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -3162,39 +3111,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3214,39 +3163,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3263,39 +3212,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -3310,39 +3259,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3358,39 +3307,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3410,39 +3359,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3462,39 +3411,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3511,39 +3460,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3563,39 +3512,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3615,39 +3564,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3664,39 +3613,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3716,39 +3665,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3762,39 +3711,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3814,39 +3763,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3863,39 +3812,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3911,39 +3860,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3963,39 +3912,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4012,39 +3961,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -4056,39 +4005,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4108,6 +4057,57 @@
  Luxembourg VAT Reg. No. LU 20260743.
  This email is sent from an unmonitored email address.
  SPC-EUAmazon-439806292595808</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 5 May 2026 17:50:39 +0000</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 06/03/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0DRTR7GYJ
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-1583298956134227</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5844,71 +5844,21 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
+          <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 3 May 2026 05:32:15 +0000</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5930,39 +5880,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -5988,40 +5938,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6037,40 +5987,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6086,39 +6036,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6134,39 +6084,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6182,39 +6132,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6230,39 +6180,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6276,39 +6226,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -6326,40 +6276,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6375,39 +6325,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6423,39 +6373,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6471,40 +6421,40 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6520,39 +6470,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6569,39 +6519,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -6630,39 +6580,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6678,39 +6628,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6724,39 +6674,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6771,39 +6721,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6823,39 +6773,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -6884,40 +6834,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -6930,39 +6880,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -6977,39 +6927,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -7022,40 +6972,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -7070,40 +7020,40 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -7117,39 +7067,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -7163,39 +7113,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -7210,39 +7160,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -7256,39 +7206,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -7303,39 +7253,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7350,39 +7300,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7401,39 +7351,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7449,39 +7399,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7502,39 +7452,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7552,40 +7502,40 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7603,39 +7553,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7652,39 +7602,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7702,40 +7652,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7753,39 +7703,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7803,39 +7753,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7852,39 +7802,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7899,39 +7849,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7950,39 +7900,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -8000,39 +7950,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -8071,39 +8021,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -8119,40 +8069,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -8168,39 +8118,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -8216,39 +8166,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -8262,40 +8212,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -8311,39 +8261,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -8359,39 +8309,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8412,39 +8362,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8459,39 +8409,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -8508,39 +8458,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -8554,39 +8504,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -8605,40 +8555,40 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -8652,39 +8602,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8708,39 +8658,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8764,39 +8714,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8817,39 +8767,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8871,39 +8821,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8926,39 +8876,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8979,39 +8929,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9034,39 +8984,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9096,39 +9046,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -9177,39 +9127,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -9218,39 +9168,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
